--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,6 +293,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,6 +437,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -474,7 +481,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -554,7 +561,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -587,7 +594,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -693,72 +700,72 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -783,7 +790,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -824,7 +831,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -882,7 +889,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -913,7 +920,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -966,7 +973,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1105,10 +1112,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1228,7 +1235,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1394,7 +1401,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1416,7 +1423,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1431,10 +1438,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1478,7 +1489,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2111,7 +2122,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2119,10 +2130,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2133,7 +2144,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2142,19 +2153,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2204,13 +2215,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2239,10 +2250,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2253,7 +2264,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2262,16 +2273,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2322,19 +2333,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2357,10 +2368,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2371,28 +2382,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2442,19 +2453,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2477,10 +2488,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2491,7 +2502,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2503,16 +2514,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2538,13 +2549,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2562,19 +2573,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2597,21 +2608,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2623,16 +2634,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2682,19 +2693,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2706,7 +2717,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2717,14 +2728,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2743,16 +2754,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2802,7 +2813,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2814,7 +2825,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2826,7 +2837,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2837,14 +2848,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2863,16 +2874,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2922,7 +2933,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2934,7 +2945,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2946,7 +2957,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2957,14 +2968,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2977,25 +2988,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3044,7 +3055,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3056,7 +3067,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3068,7 +3079,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3079,10 +3090,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3102,20 +3113,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3164,7 +3175,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3176,22 +3187,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3199,14 +3210,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3222,20 +3233,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3284,7 +3295,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3296,19 +3307,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3319,14 +3330,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3342,19 +3353,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3404,7 +3415,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3416,19 +3427,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3439,10 +3450,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3450,34 +3461,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3502,13 +3513,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3526,34 +3537,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3561,10 +3572,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3587,19 +3598,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3624,13 +3635,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3648,7 +3659,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3660,7 +3671,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3672,10 +3683,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3683,21 +3694,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3706,22 +3717,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3731,7 +3742,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3746,13 +3757,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3770,45 +3781,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3819,7 +3830,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3831,13 +3842,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>216</v>
+        <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3888,13 +3899,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3912,7 +3923,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3923,14 +3934,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3949,16 +3960,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3996,19 +4007,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4020,7 +4031,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4032,7 +4043,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4043,10 +4054,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4066,22 +4077,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4130,7 +4141,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4142,7 +4153,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4151,10 +4162,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4165,10 +4176,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4179,7 +4190,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4188,22 +4199,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4252,19 +4263,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4273,10 +4284,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4287,10 +4298,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4298,10 +4309,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4310,22 +4321,22 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4374,34 +4385,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4409,10 +4420,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4432,19 +4443,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4494,7 +4505,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4506,7 +4517,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4515,13 +4526,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4529,21 +4540,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4552,22 +4563,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4616,34 +4627,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4651,21 +4662,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4674,22 +4685,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4738,34 +4749,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4773,10 +4784,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4787,7 +4798,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4796,19 +4807,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4858,19 +4869,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4879,13 +4890,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4893,10 +4904,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4916,20 +4927,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4978,7 +4989,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4990,22 +5001,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5013,10 +5024,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5024,10 +5035,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5036,22 +5047,22 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5088,68 +5099,68 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5158,22 +5169,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5222,45 +5233,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5271,7 +5282,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5283,19 +5294,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5320,13 +5331,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5344,19 +5355,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5365,10 +5376,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5379,14 +5390,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5405,19 +5416,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5442,13 +5453,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5466,7 +5477,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5478,33 +5489,33 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5518,7 +5529,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5527,19 +5538,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5588,7 +5599,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5600,7 +5611,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5609,10 +5620,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5623,10 +5634,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5637,7 +5648,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5649,16 +5660,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5684,13 +5695,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5708,45 +5719,45 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5757,7 +5768,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5769,19 +5780,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5806,13 +5817,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5830,19 +5841,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5851,10 +5862,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5865,10 +5876,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5879,7 +5890,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5891,16 +5902,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5950,45 +5961,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5999,7 +6010,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6011,16 +6022,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6070,45 +6081,45 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6131,19 +6142,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6192,7 +6203,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6204,7 +6215,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6213,10 +6224,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6227,10 +6238,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6241,7 +6252,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6253,13 +6264,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6310,13 +6321,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6334,7 +6345,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6345,14 +6356,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6371,16 +6382,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6430,7 +6441,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6442,7 +6453,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6454,7 +6465,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6465,14 +6476,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6485,25 +6496,25 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6552,7 +6563,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6564,7 +6575,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6576,7 +6587,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6587,10 +6598,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6601,7 +6612,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6613,13 +6624,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6670,19 +6681,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6691,10 +6702,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6705,10 +6716,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6719,7 +6730,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6731,13 +6742,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6788,31 +6799,31 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6823,10 +6834,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6837,7 +6848,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6849,19 +6860,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6886,13 +6897,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6910,31 +6921,31 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6945,10 +6956,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6971,19 +6982,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7008,13 +7019,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7032,7 +7043,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7044,19 +7055,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7067,10 +7078,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7081,7 +7092,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7093,17 +7104,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7152,19 +7163,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7176,7 +7187,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7187,10 +7198,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7201,7 +7212,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7213,13 +7224,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7270,19 +7281,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7291,10 +7302,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7305,10 +7316,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7328,19 +7339,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7390,7 +7401,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7402,7 +7413,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7411,10 +7422,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7425,10 +7436,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7448,19 +7459,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7510,7 +7521,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7522,7 +7533,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7531,10 +7542,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7545,10 +7556,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7568,22 +7579,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7632,7 +7643,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7644,7 +7655,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>454</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7653,10 +7664,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7667,10 +7678,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7681,7 +7692,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7693,13 +7704,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7750,13 +7761,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7774,7 +7785,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7785,14 +7796,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7811,16 +7822,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7870,7 +7881,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7882,7 +7893,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7905,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7905,14 +7916,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7925,25 +7936,25 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7992,7 +8003,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8004,7 +8015,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8016,7 +8027,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8027,10 +8038,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8038,10 +8049,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8050,22 +8061,22 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8090,13 +8101,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8114,34 +8125,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8149,10 +8160,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8163,7 +8174,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8172,22 +8183,22 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8236,45 +8247,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8285,7 +8296,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8297,19 +8308,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8334,13 +8345,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8358,19 +8369,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8379,10 +8390,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8393,14 +8404,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8419,19 +8430,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8456,13 +8467,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8480,7 +8491,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8492,33 +8503,33 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8544,16 +8555,16 @@
         <v>83</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8602,7 +8613,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8614,7 +8625,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8623,10 +8634,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="475">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,9 +293,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -437,10 +434,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -481,7 +474,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -561,7 +554,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -594,7 +587,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -700,6 +693,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -762,10 +759,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -790,7 +783,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -831,7 +824,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -889,7 +882,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -920,7 +913,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -973,7 +966,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1112,10 +1105,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1235,7 +1228,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1401,7 +1394,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1423,7 +1416,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1438,14 +1431,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1489,7 +1478,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2122,7 +2111,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2130,10 +2119,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2144,28 +2133,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2215,13 +2204,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2250,10 +2239,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2264,25 +2253,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2333,19 +2322,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2368,10 +2357,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2382,28 +2371,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2453,19 +2442,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2488,10 +2477,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2502,7 +2491,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2514,16 +2503,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2549,43 +2538,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2608,21 +2597,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2634,16 +2623,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2693,31 +2682,31 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2728,14 +2717,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2754,16 +2743,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2813,7 +2802,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2825,7 +2814,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2837,7 +2826,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2848,14 +2837,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2874,16 +2863,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2933,7 +2922,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2945,7 +2934,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2957,7 +2946,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2968,14 +2957,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2988,25 +2977,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3055,7 +3044,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3067,7 +3056,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3079,7 +3068,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3090,10 +3079,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3113,20 +3102,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3175,7 +3164,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3187,22 +3176,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3210,14 +3199,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3233,20 +3222,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3295,7 +3284,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3307,19 +3296,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3330,14 +3319,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3353,19 +3342,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3415,7 +3404,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3427,19 +3416,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3450,10 +3439,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3461,34 +3450,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3513,58 +3502,58 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3572,10 +3561,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3598,19 +3587,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3635,13 +3624,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3659,7 +3648,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3671,7 +3660,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3683,10 +3672,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3694,45 +3683,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3742,84 +3731,84 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3830,7 +3819,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3842,13 +3831,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3899,31 +3888,31 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3934,14 +3923,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3960,16 +3949,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4007,19 +3996,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4031,7 +4020,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4043,7 +4032,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4054,10 +4043,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4077,22 +4066,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4141,7 +4130,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4153,7 +4142,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4162,10 +4151,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4176,10 +4165,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4190,31 +4179,31 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4263,31 +4252,31 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4298,10 +4287,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4309,34 +4298,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4385,34 +4374,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4420,10 +4409,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4443,19 +4432,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4505,7 +4494,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4517,7 +4506,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4526,13 +4515,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4540,45 +4529,45 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4627,34 +4616,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4662,45 +4651,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4749,34 +4738,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4784,10 +4773,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4798,28 +4787,28 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4869,19 +4858,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4890,13 +4879,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4904,10 +4893,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4927,20 +4916,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4989,7 +4978,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5001,22 +4990,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5024,10 +5013,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5035,34 +5024,34 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5099,92 +5088,92 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AF27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5233,45 +5222,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5282,7 +5271,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5294,19 +5283,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5331,55 +5320,55 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AJ29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5390,14 +5379,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5416,19 +5405,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5453,13 +5442,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5477,7 +5466,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5489,33 +5478,33 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5529,7 +5518,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5538,19 +5527,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5599,7 +5588,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5611,7 +5600,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5620,10 +5609,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5634,10 +5623,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5648,7 +5637,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5660,16 +5649,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5695,69 +5684,69 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5768,7 +5757,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5780,19 +5769,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5817,55 +5806,55 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5876,10 +5865,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5890,7 +5879,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5902,16 +5891,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5961,45 +5950,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>373</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6010,7 +5999,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6022,16 +6011,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6081,45 +6070,45 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6142,19 +6131,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6203,7 +6192,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6215,19 +6204,19 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6238,10 +6227,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6252,7 +6241,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6264,13 +6253,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6321,31 +6310,31 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6356,14 +6345,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6382,16 +6371,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6441,7 +6430,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6453,7 +6442,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6465,7 +6454,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6476,14 +6465,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6496,25 +6485,25 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6563,7 +6552,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6575,7 +6564,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6587,7 +6576,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6598,10 +6587,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6612,7 +6601,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6624,13 +6613,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6681,31 +6670,31 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6716,10 +6705,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6730,7 +6719,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6742,13 +6731,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6799,19 +6788,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6820,10 +6809,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6834,10 +6823,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6848,7 +6837,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6860,19 +6849,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6897,55 +6886,55 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6956,10 +6945,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6982,19 +6971,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7019,13 +7008,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7043,7 +7032,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7055,19 +7044,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7078,10 +7067,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7092,7 +7081,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7104,17 +7093,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7163,19 +7152,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7187,7 +7176,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7198,10 +7187,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7212,7 +7201,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7224,13 +7213,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7281,19 +7270,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7302,10 +7291,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7316,10 +7305,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7339,19 +7328,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7401,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7413,7 +7402,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7422,10 +7411,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7436,10 +7425,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7459,19 +7448,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7521,7 +7510,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7533,7 +7522,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7542,10 +7531,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7556,10 +7545,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7579,22 +7568,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7643,7 +7632,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7655,7 +7644,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>454</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7664,10 +7653,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7678,10 +7667,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7692,7 +7681,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7704,13 +7693,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7761,31 +7750,31 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7796,14 +7785,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7822,16 +7811,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7881,7 +7870,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7893,7 +7882,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7905,7 +7894,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7916,14 +7905,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7936,25 +7925,25 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8003,7 +7992,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8015,7 +8004,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8027,7 +8016,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8038,10 +8027,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8049,34 +8038,34 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G52" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8101,14 +8090,14 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8125,34 +8114,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8160,10 +8149,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8174,31 +8163,31 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8247,45 +8236,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8296,7 +8285,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8308,19 +8297,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8345,55 +8334,55 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Z54" t="s" s="2">
+      <c r="AJ54" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8404,14 +8393,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8430,19 +8419,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8467,13 +8456,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8491,7 +8480,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8503,33 +8492,33 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8555,16 +8544,16 @@
         <v>83</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8613,7 +8602,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8625,7 +8614,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8634,10 +8623,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-breastfeeding.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
